--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
   <si>
     <t>Mat</t>
   </si>
@@ -94,10 +94,112 @@
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>AYALA</t>
+  </si>
+  <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>RAYMUNDO</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
+    <t>MENDOZA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>QUETZALY</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>ESTEPHANY</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
   </si>
 </sst>
 </file>
@@ -1097,7 +1199,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1135,10 +1237,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1147,6 +1249,282 @@
         <v>14</v>
       </c>
       <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>22330051920290</v>
+      </c>
+      <c r="B3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F3" t="s">
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>22330051920294</v>
+      </c>
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" t="s">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>22330051920412</v>
+      </c>
+      <c r="B5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D5" t="s">
+        <v>51</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>22330051920297</v>
+      </c>
+      <c r="B6" t="s">
+        <v>28</v>
+      </c>
+      <c r="C6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D6" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" t="s">
+        <v>10</v>
+      </c>
+      <c r="F6" t="s">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>22330051920298</v>
+      </c>
+      <c r="B7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>22330051920302</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s">
+        <v>42</v>
+      </c>
+      <c r="D8" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>22330051920303</v>
+      </c>
+      <c r="B9" t="s">
+        <v>31</v>
+      </c>
+      <c r="C9" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" t="s">
+        <v>55</v>
+      </c>
+      <c r="E9" t="s">
+        <v>10</v>
+      </c>
+      <c r="F9" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
+        <v>22330051920419</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="D10" t="s">
+        <v>56</v>
+      </c>
+      <c r="E10" t="s">
+        <v>10</v>
+      </c>
+      <c r="F10" t="s">
+        <v>16</v>
+      </c>
+      <c r="G10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11">
+        <v>22330051920308</v>
+      </c>
+      <c r="B11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C11" t="s">
+        <v>31</v>
+      </c>
+      <c r="D11" t="s">
+        <v>57</v>
+      </c>
+      <c r="E11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F11" t="s">
+        <v>16</v>
+      </c>
+      <c r="G11">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12">
+        <v>22330051920312</v>
+      </c>
+      <c r="B12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C12" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" t="s">
+        <v>58</v>
+      </c>
+      <c r="E12" t="s">
+        <v>10</v>
+      </c>
+      <c r="F12" t="s">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13">
+        <v>22330051920364</v>
+      </c>
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="s">
+        <v>46</v>
+      </c>
+      <c r="D13" t="s">
+        <v>59</v>
+      </c>
+      <c r="E13" t="s">
+        <v>10</v>
+      </c>
+      <c r="F13" t="s">
+        <v>16</v>
+      </c>
+      <c r="G13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14">
+        <v>22330051920397</v>
+      </c>
+      <c r="B14" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" t="s">
+        <v>47</v>
+      </c>
+      <c r="D14" t="s">
+        <v>60</v>
+      </c>
+      <c r="E14" t="s">
+        <v>10</v>
+      </c>
+      <c r="F14" t="s">
+        <v>16</v>
+      </c>
+      <c r="G14">
         <v>2</v>
       </c>
     </row>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="65">
   <si>
     <t>Mat</t>
   </si>
@@ -91,115 +91,127 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>CESAR</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>ELIZALDE</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LIBRADO</t>
+  </si>
+  <si>
+    <t>MALDONADO</t>
+  </si>
+  <si>
+    <t>PANTOJA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>AYALA</t>
   </si>
   <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
     <t>RAYMUNDO</t>
   </si>
   <si>
-    <t>SANTOS</t>
+    <t>CHIPAHUA</t>
   </si>
   <si>
     <t>LOPEZ</t>
   </si>
   <si>
+    <t>ANTONIO</t>
+  </si>
+  <si>
+    <t>CARBAJAL</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>CORTES</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>CORTES</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
     <t>MENDOZA</t>
   </si>
   <si>
-    <t>RODRIGUEZ</t>
+    <t>OSCAR</t>
   </si>
   <si>
     <t>QUETZALY</t>
   </si>
   <si>
+    <t>LUIS GUSTAVO</t>
+  </si>
+  <si>
+    <t>MIA NOEMI</t>
+  </si>
+  <si>
+    <t>PABLO</t>
+  </si>
+  <si>
+    <t>JOSE CARMELO</t>
+  </si>
+  <si>
+    <t>ABDIEL ARMANDO</t>
+  </si>
+  <si>
+    <t>ANGEL DE JESUS</t>
+  </si>
+  <si>
+    <t>LESLIE YAMILET</t>
+  </si>
+  <si>
+    <t>DIEGO</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
+  </si>
+  <si>
     <t>MARCOS</t>
   </si>
   <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
     <t>ESTEPHANY</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
   </si>
 </sst>
 </file>
@@ -1199,7 +1211,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1231,16 +1243,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920285</v>
+        <v>22330051920277</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1254,22 +1266,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920290</v>
+        <v>22330051920285</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1286,7 +1298,7 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1306,10 +1318,10 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1329,10 +1341,10 @@
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1352,10 +1364,10 @@
         <v>29</v>
       </c>
       <c r="C7" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E7" t="s">
         <v>10</v>
@@ -1375,10 +1387,10 @@
         <v>30</v>
       </c>
       <c r="C8" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E8" t="s">
         <v>10</v>
@@ -1398,10 +1410,10 @@
         <v>31</v>
       </c>
       <c r="C9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
@@ -1415,7 +1427,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>22330051920419</v>
+        <v>22330051920417</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
@@ -1424,7 +1436,7 @@
         <v>44</v>
       </c>
       <c r="D10" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="E10" t="s">
         <v>10</v>
@@ -1438,16 +1450,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>22330051920308</v>
+        <v>22330051920419</v>
       </c>
       <c r="B11" t="s">
         <v>33</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D11" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
@@ -1461,16 +1473,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>22330051920312</v>
+        <v>22330051920308</v>
       </c>
       <c r="B12" t="s">
         <v>34</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E12" t="s">
         <v>10</v>
@@ -1484,16 +1496,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>22330051920364</v>
+        <v>22330051920312</v>
       </c>
       <c r="B13" t="s">
         <v>35</v>
       </c>
       <c r="C13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
@@ -1513,10 +1525,10 @@
         <v>36</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="D14" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E14" t="s">
         <v>10</v>
@@ -1526,6 +1538,52 @@
       </c>
       <c r="G14">
         <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
+      <c r="A15">
+        <v>22330051920290</v>
+      </c>
+      <c r="B15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C15" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E15" t="s">
+        <v>10</v>
+      </c>
+      <c r="F15" t="s">
+        <v>16</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7">
+      <c r="A16">
+        <v>22330051920364</v>
+      </c>
+      <c r="B16" t="s">
+        <v>38</v>
+      </c>
+      <c r="C16" t="s">
+        <v>49</v>
+      </c>
+      <c r="D16" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" t="s">
+        <v>10</v>
+      </c>
+      <c r="F16" t="s">
+        <v>16</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
@@ -635,7 +635,7 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -644,13 +644,13 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>92.86</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -853,13 +853,13 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1056,7 +1056,7 @@
         <v>13</v>
       </c>
       <c r="C3">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D3">
         <v>0</v>
@@ -1065,13 +1065,13 @@
         <v>3</v>
       </c>
       <c r="F3">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>92.86</v>
+        <v>92.68000000000001</v>
       </c>
       <c r="H3">
-        <v>7.1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="65">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="38">
   <si>
     <t>Mat</t>
   </si>
@@ -94,124 +94,43 @@
     <t>RODRIGUEZ</t>
   </si>
   <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>COLOHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>ELIZALDE</t>
-  </si>
-  <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>LIBRADO</t>
   </si>
   <si>
     <t>MALDONADO</t>
   </si>
   <si>
-    <t>PANTOJA</t>
-  </si>
-  <si>
     <t>QUESADA</t>
   </si>
   <si>
     <t>SANTOS</t>
   </si>
   <si>
-    <t>AYALA</t>
-  </si>
-  <si>
-    <t>RAYMUNDO</t>
-  </si>
-  <si>
     <t>CHIPAHUA</t>
   </si>
   <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>ANTONIO</t>
-  </si>
-  <si>
-    <t>CARBAJAL</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>MARTINEZ</t>
   </si>
   <si>
     <t>OLGUIN</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>MENDOZA</t>
-  </si>
-  <si>
     <t>OSCAR</t>
   </si>
   <si>
-    <t>QUETZALY</t>
-  </si>
-  <si>
-    <t>LUIS GUSTAVO</t>
-  </si>
-  <si>
-    <t>MIA NOEMI</t>
-  </si>
-  <si>
-    <t>PABLO</t>
-  </si>
-  <si>
-    <t>JOSE CARMELO</t>
-  </si>
-  <si>
-    <t>ABDIEL ARMANDO</t>
-  </si>
-  <si>
-    <t>ANGEL DE JESUS</t>
-  </si>
-  <si>
     <t>LESLIE YAMILET</t>
   </si>
   <si>
     <t>DIEGO</t>
   </si>
   <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
     <t>JARED DE JESUS</t>
   </si>
   <si>
     <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>ESTEPHANY</t>
   </si>
 </sst>
 </file>
@@ -687,10 +606,10 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -699,7 +618,7 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>96.88</v>
+        <v>93.94</v>
       </c>
       <c r="H5">
         <v>7.3</v>
@@ -879,16 +798,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="E4">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>63.33</v>
+      </c>
+      <c r="H4">
+        <v>6.1</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -899,10 +821,10 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
         <v>32</v>
@@ -925,16 +847,19 @@
         <v>33</v>
       </c>
       <c r="D6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E6">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H6">
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -948,16 +873,19 @@
         <v>33</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>84.84999999999999</v>
+      </c>
+      <c r="H7">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -971,16 +899,19 @@
         <v>17</v>
       </c>
       <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8">
+        <v>0</v>
+      </c>
+      <c r="F8">
         <v>17</v>
       </c>
-      <c r="E8">
-        <v>17</v>
-      </c>
-      <c r="F8">
-        <v>0</v>
-      </c>
       <c r="G8">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H8">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -1088,16 +1019,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F4">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G4">
-        <v>60</v>
+        <v>63.33</v>
       </c>
       <c r="H4">
-        <v>6.1</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1108,10 +1039,10 @@
         <v>15</v>
       </c>
       <c r="C5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>1</v>
@@ -1120,7 +1051,7 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>96.88</v>
+        <v>93.94</v>
       </c>
       <c r="H5">
         <v>7.3</v>
@@ -1149,7 +1080,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>7.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1166,16 +1097,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F7">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>57.58</v>
+        <v>84.84999999999999</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1201,7 +1132,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
     </row>
   </sheetData>
@@ -1211,7 +1142,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1249,10 +1180,10 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>39</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1266,22 +1197,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920285</v>
+        <v>22330051920417</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>2</v>
@@ -1289,7 +1220,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920294</v>
+        <v>22330051920419</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
@@ -1298,7 +1229,7 @@
         <v>31</v>
       </c>
       <c r="D4" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="E4" t="s">
         <v>10</v>
@@ -1312,16 +1243,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920412</v>
+        <v>22330051920312</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -1335,16 +1266,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920297</v>
+        <v>22330051920397</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
@@ -1354,236 +1285,6 @@
       </c>
       <c r="G6">
         <v>2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920298</v>
-      </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>43</v>
-      </c>
-      <c r="D7" t="s">
-        <v>55</v>
-      </c>
-      <c r="E7" t="s">
-        <v>10</v>
-      </c>
-      <c r="F7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920302</v>
-      </c>
-      <c r="B8" t="s">
-        <v>30</v>
-      </c>
-      <c r="C8" t="s">
-        <v>44</v>
-      </c>
-      <c r="D8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920303</v>
-      </c>
-      <c r="B9" t="s">
-        <v>31</v>
-      </c>
-      <c r="C9" t="s">
-        <v>45</v>
-      </c>
-      <c r="D9" t="s">
-        <v>57</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920417</v>
-      </c>
-      <c r="B10" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="D10" t="s">
-        <v>58</v>
-      </c>
-      <c r="E10" t="s">
-        <v>10</v>
-      </c>
-      <c r="F10" t="s">
-        <v>16</v>
-      </c>
-      <c r="G10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920419</v>
-      </c>
-      <c r="B11" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>59</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>16</v>
-      </c>
-      <c r="G11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920308</v>
-      </c>
-      <c r="B12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>60</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>16</v>
-      </c>
-      <c r="G12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920312</v>
-      </c>
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" t="s">
-        <v>61</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>16</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920397</v>
-      </c>
-      <c r="B14" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" t="s">
-        <v>24</v>
-      </c>
-      <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
-        <v>16</v>
-      </c>
-      <c r="G14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920290</v>
-      </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>48</v>
-      </c>
-      <c r="D15" t="s">
-        <v>63</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920364</v>
-      </c>
-      <c r="B16" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" t="s">
-        <v>64</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>16</v>
-      </c>
-      <c r="G16">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
@@ -91,19 +91,25 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>QUESADA</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
     <t>LIBRADO</t>
   </si>
   <si>
-    <t>MALDONADO</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
+    <t>FIERROS</t>
+  </si>
+  <si>
+    <t>OLGUIN</t>
   </si>
   <si>
     <t>CHIPAHUA</t>
@@ -112,25 +118,19 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
+    <t>MIA</t>
+  </si>
+  <si>
+    <t>JARED DE JESUS</t>
+  </si>
+  <si>
+    <t>AZUL MARIAM</t>
   </si>
   <si>
     <t>OSCAR</t>
   </si>
   <si>
     <t>LESLIE YAMILET</t>
-  </si>
-  <si>
-    <t>DIEGO</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
   </si>
 </sst>
 </file>
@@ -609,19 +609,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -752,16 +752,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>39</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>97.44</v>
+      </c>
+      <c r="H2">
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -824,16 +827,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>1</v>
       </c>
       <c r="E5">
+        <v>1</v>
+      </c>
+      <c r="F5">
         <v>32</v>
       </c>
-      <c r="F5">
-        <v>0</v>
-      </c>
       <c r="G5">
-        <v>0</v>
+        <v>96.97</v>
+      </c>
+      <c r="H5">
+        <v>7.3</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -967,16 +973,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G2">
-        <v>94.87</v>
+        <v>97.44</v>
       </c>
       <c r="H2">
-        <v>7.4</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1042,19 +1048,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>93.94</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1174,7 +1180,7 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920277</v>
+        <v>22330051920263</v>
       </c>
       <c r="B2" t="s">
         <v>24</v>
@@ -1197,7 +1203,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920417</v>
+        <v>22330051920312</v>
       </c>
       <c r="B3" t="s">
         <v>25</v>
@@ -1220,13 +1226,13 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920419</v>
+        <v>22330051920397</v>
       </c>
       <c r="B4" t="s">
         <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s">
         <v>35</v>
@@ -1243,36 +1249,36 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920312</v>
+        <v>22330051920277</v>
       </c>
       <c r="B5" t="s">
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>36</v>
       </c>
       <c r="E5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920397</v>
+        <v>22330051920417</v>
       </c>
       <c r="B6" t="s">
         <v>28</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
         <v>37</v>
@@ -1284,7 +1290,7 @@
         <v>16</v>
       </c>
       <c r="G6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
@@ -778,16 +778,19 @@
         <v>41</v>
       </c>
       <c r="D3">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>41</v>
+        <v>3</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>92.68000000000001</v>
+      </c>
+      <c r="H3">
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -801,7 +804,7 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>11</v>
@@ -827,19 +830,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1008,7 +1011,7 @@
         <v>92.68000000000001</v>
       </c>
       <c r="H3">
-        <v>7</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="4" spans="1:8">

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
@@ -1141,7 +1141,7 @@
         <v>100</v>
       </c>
       <c r="H8">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="24">
   <si>
     <t>Mat</t>
   </si>
@@ -89,48 +89,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>QUESADA</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>LIBRADO</t>
-  </si>
-  <si>
-    <t>FIERROS</t>
-  </si>
-  <si>
-    <t>OLGUIN</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>JARED DE JESUS</t>
-  </si>
-  <si>
-    <t>AZUL MARIAM</t>
-  </si>
-  <si>
-    <t>OSCAR</t>
-  </si>
-  <si>
-    <t>LESLIE YAMILET</t>
   </si>
 </sst>
 </file>
@@ -976,16 +934,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>97.44</v>
+        <v>92.31</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1011,7 +969,7 @@
         <v>92.68000000000001</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1028,16 +986,16 @@
         <v>0</v>
       </c>
       <c r="E4">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G4">
-        <v>63.33</v>
+        <v>86.67</v>
       </c>
       <c r="H4">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1063,7 +1021,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1089,7 +1047,7 @@
         <v>100</v>
       </c>
       <c r="H6">
-        <v>8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1106,16 +1064,16 @@
         <v>0</v>
       </c>
       <c r="E7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="G7">
-        <v>84.84999999999999</v>
+        <v>96.97</v>
       </c>
       <c r="H7">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
     </row>
     <row r="8" spans="1:8">
@@ -1151,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1181,121 +1139,6 @@
         <v>23</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920263</v>
-      </c>
-      <c r="B2" t="s">
-        <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D2" t="s">
-        <v>33</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>22330051920312</v>
-      </c>
-      <c r="B3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>30</v>
-      </c>
-      <c r="D3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E3" t="s">
-        <v>10</v>
-      </c>
-      <c r="F3" t="s">
-        <v>16</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>22330051920397</v>
-      </c>
-      <c r="B4" t="s">
-        <v>26</v>
-      </c>
-      <c r="C4" t="s">
-        <v>27</v>
-      </c>
-      <c r="D4" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>16</v>
-      </c>
-      <c r="G4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920277</v>
-      </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920417</v>
-      </c>
-      <c r="B6" t="s">
-        <v>28</v>
-      </c>
-      <c r="C6" t="s">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>16</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
+++ b/docentes/Pesce Bautista Victor Manuel - Estadisticos 20222.xlsx
@@ -960,13 +960,13 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G3">
-        <v>92.68000000000001</v>
+        <v>97.56</v>
       </c>
       <c r="H3">
         <v>7.6</v>
